--- a/artfynd/A 17223-2023 artfynd.xlsx
+++ b/artfynd/A 17223-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802575</v>
+        <v>124802573</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802573</v>
+        <v>124802575</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 17223-2023 artfynd.xlsx
+++ b/artfynd/A 17223-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802573</v>
+        <v>124802575</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802575</v>
+        <v>124802573</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 17223-2023 artfynd.xlsx
+++ b/artfynd/A 17223-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124802575</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>124802573</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>58001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 17223-2023 artfynd.xlsx
+++ b/artfynd/A 17223-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802575</v>
+        <v>124802573</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802573</v>
+        <v>124802575</v>
       </c>
       <c r="B3" t="n">
-        <v>58001</v>
+        <v>57793</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
